--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_25_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_25_6.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_0</t>
+          <t>model_25_6_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9666157635379951</v>
+        <v>0.9997587200474805</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8564611149801432</v>
+        <v>0.6581767830479786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8926572510993982</v>
+        <v>0.9994437457967154</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9643641154557735</v>
+        <v>0.9990661431711874</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9526718323452128</v>
+        <v>0.9993827674982162</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2232405429417012</v>
+        <v>0.0001432342025668207</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9598451850635749</v>
+        <v>0.2029210275768392</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3305262738900743</v>
+        <v>0.0006482656647311596</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3741217814993886</v>
+        <v>0.000210259391605409</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3523240100565809</v>
+        <v>0.0004292653040489243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3832469904473047</v>
+        <v>0.002715102243632393</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4724833784819326</v>
+        <v>0.01196804923815158</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01144602392983</v>
+        <v>1.000170315260602</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4925979740793363</v>
+        <v>0.01247755387149699</v>
       </c>
       <c r="P2" t="n">
-        <v>190.9990108419324</v>
+        <v>133.7020589744324</v>
       </c>
       <c r="Q2" t="n">
-        <v>305.5733383795433</v>
+        <v>204.3968568167881</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_1</t>
+          <t>model_25_6_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9632806713642293</v>
+        <v>0.9997600363096997</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8527047749825148</v>
+        <v>0.6581767045506146</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8510843255456195</v>
+        <v>0.9994530679550306</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9508579957971975</v>
+        <v>0.9990778082749662</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9345503020263871</v>
+        <v>0.9993924740918234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2455423196643604</v>
+        <v>0.0001424528124539728</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9849638479240708</v>
+        <v>0.2029210741762653</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4585362635608612</v>
+        <v>0.00063740150384692</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5159151903746294</v>
+        <v>0.0002076329744203644</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4872257091221427</v>
+        <v>0.0004225146811572209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4084956145025384</v>
+        <v>0.002776022101191064</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4955222695947785</v>
+        <v>0.0119353597538563</v>
       </c>
       <c r="N3" t="n">
-        <v>1.012589484103693</v>
+        <v>1.00016938613433</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5166176784839354</v>
+        <v>0.0124434727281787</v>
       </c>
       <c r="P3" t="n">
-        <v>190.8085719301573</v>
+        <v>133.7129995075372</v>
       </c>
       <c r="Q3" t="n">
-        <v>305.3828994677681</v>
+        <v>204.4077973498929</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_2</t>
+          <t>model_25_6_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9593105149868039</v>
+        <v>0.9997611890339365</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8482344202501665</v>
+        <v>0.6581763544500314</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8090481169335572</v>
+        <v>0.9994633688239222</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9372986174466055</v>
+        <v>0.9990906986863142</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9162954030969122</v>
+        <v>0.9994031874196697</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2720907736410932</v>
+        <v>0.0001417685055518863</v>
       </c>
       <c r="H4" t="n">
-        <v>1.014857130603375</v>
+        <v>0.202921282011095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5879727792390332</v>
+        <v>0.0006253967413123566</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6582677333079185</v>
+        <v>0.0002047306772331086</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6231202411252141</v>
+        <v>0.0004150639070614864</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4300189551357453</v>
+        <v>0.002843644964382352</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5216232104125479</v>
+        <v>0.01190665803455723</v>
       </c>
       <c r="N4" t="n">
-        <v>1.013950680575953</v>
+        <v>1.000168572446633</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5438297903887132</v>
+        <v>0.01241354911726831</v>
       </c>
       <c r="P4" t="n">
-        <v>190.6032390834776</v>
+        <v>133.7226301464936</v>
       </c>
       <c r="Q4" t="n">
-        <v>305.1775666210885</v>
+        <v>204.4174279888493</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_3</t>
+          <t>model_25_6_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9549980095462173</v>
+        <v>0.9997620869704489</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8433770610004006</v>
+        <v>0.6581753533108127</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7677070138917597</v>
+        <v>0.9994747559769759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9240732917949293</v>
+        <v>0.9991048269056743</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8984198097567946</v>
+        <v>0.9994150155158515</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3009285173795574</v>
+        <v>0.000141235451649282</v>
       </c>
       <c r="H5" t="n">
-        <v>1.047338314272642</v>
+        <v>0.2029218763305822</v>
       </c>
       <c r="I5" t="n">
-        <v>0.715268948629701</v>
+        <v>0.0006121260095135691</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7971132385338101</v>
+        <v>0.0002015496855484371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7561911170921154</v>
+        <v>0.0004068378475310031</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4484698430842361</v>
+        <v>0.002918518374001289</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5485695191856338</v>
+        <v>0.01188425225452918</v>
       </c>
       <c r="N5" t="n">
-        <v>1.015429253869868</v>
+        <v>1.000167938609095</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5719232593128183</v>
+        <v>0.01239018947679811</v>
       </c>
       <c r="P5" t="n">
-        <v>190.4017650524517</v>
+        <v>133.730164380831</v>
       </c>
       <c r="Q5" t="n">
-        <v>304.9760925900625</v>
+        <v>204.4249622231867</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_4</t>
+          <t>model_25_6_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9505452554075212</v>
+        <v>0.9997626127417021</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8383595374584971</v>
+        <v>0.6581736859502079</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7277820173587142</v>
+        <v>0.9994873192262348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9114180871755322</v>
+        <v>0.999120426819333</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8812391088362035</v>
+        <v>0.9994280669585744</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3307041048080659</v>
+        <v>0.0001409233311212606</v>
       </c>
       <c r="H6" t="n">
-        <v>1.080890517300922</v>
+        <v>0.2029228661478635</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8382046892763397</v>
+        <v>0.0005974846403626515</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9299733529382156</v>
+        <v>0.000198037339486611</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8840890211072776</v>
+        <v>0.0003977609899246312</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4643722617762859</v>
+        <v>0.003001623369819295</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5750687826756604</v>
+        <v>0.01187111330588924</v>
       </c>
       <c r="N6" t="n">
-        <v>1.016955912431707</v>
+        <v>1.000167567476446</v>
       </c>
       <c r="O6" t="n">
-        <v>0.599550651310653</v>
+        <v>0.01237649117591319</v>
       </c>
       <c r="P6" t="n">
-        <v>190.2130624931772</v>
+        <v>133.7345891327706</v>
       </c>
       <c r="Q6" t="n">
-        <v>304.7873900307881</v>
+        <v>204.4293869751262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_5</t>
+          <t>model_25_6_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9460915745295678</v>
+        <v>0.9997626061321959</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8333387758237432</v>
+        <v>0.6581712452985591</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6897121038774217</v>
+        <v>0.9995011571962998</v>
       </c>
       <c r="E7" t="n">
-        <v>0.899468413004911</v>
+        <v>0.9991375386093239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8649395575449007</v>
+        <v>0.999442430595722</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3604858893462551</v>
+        <v>0.0001409272548096353</v>
       </c>
       <c r="H7" t="n">
-        <v>1.114464373471004</v>
+        <v>0.2029243150241129</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9554283189966943</v>
+        <v>0.0005813576955058816</v>
       </c>
       <c r="J7" t="n">
-        <v>1.055426486660818</v>
+        <v>0.0001941845919971145</v>
       </c>
       <c r="K7" t="n">
-        <v>1.005427402828756</v>
+        <v>0.0003877715434039683</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4781595666420232</v>
+        <v>0.003093901279599201</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6004047712554049</v>
+        <v>0.01187127856676084</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01848288873272</v>
+        <v>1.000167572141979</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6259652453769639</v>
+        <v>0.01237666347228223</v>
       </c>
       <c r="P7" t="n">
-        <v>190.0406049298397</v>
+        <v>133.7345334481125</v>
       </c>
       <c r="Q7" t="n">
-        <v>304.6149324674506</v>
+        <v>204.4293312904682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_6</t>
+          <t>model_25_6_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9417309506082167</v>
+        <v>0.999761869742238</v>
       </c>
       <c r="C8" t="n">
-        <v>0.828421872035273</v>
+        <v>0.6581678092534451</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6537413312206847</v>
+        <v>0.9995163905049594</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8882910759277164</v>
+        <v>0.9991562732595134</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8496187414698072</v>
+        <v>0.9994582268890664</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3896454015871569</v>
+        <v>0.0001413644076990487</v>
       </c>
       <c r="H8" t="n">
-        <v>1.147343731744764</v>
+        <v>0.202926354808922</v>
       </c>
       <c r="I8" t="n">
-        <v>1.066188343096576</v>
+        <v>0.000563604605451065</v>
       </c>
       <c r="J8" t="n">
-        <v>1.172771273053013</v>
+        <v>0.0001899664548809771</v>
       </c>
       <c r="K8" t="n">
-        <v>1.119479808074795</v>
+        <v>0.0003767857306903644</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4901707450355381</v>
+        <v>0.00319602830443322</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6242158293308148</v>
+        <v>0.01188967651784727</v>
       </c>
       <c r="N8" t="n">
-        <v>1.019977959791469</v>
+        <v>1.000168091946656</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6507899894903291</v>
+        <v>0.01239584466223542</v>
       </c>
       <c r="P8" t="n">
-        <v>189.8850363603107</v>
+        <v>133.7283390995444</v>
       </c>
       <c r="Q8" t="n">
-        <v>304.4593638979215</v>
+        <v>204.4231369419001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_7</t>
+          <t>model_25_6_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9375265656505153</v>
+        <v>0.999760149412208</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8236807829454795</v>
+        <v>0.6581633764689447</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6199955415542926</v>
+        <v>0.9995331286002486</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8779089472104679</v>
+        <v>0.9991767678227838</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8353188139342984</v>
+        <v>0.999475569156156</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4177601431587188</v>
+        <v>0.0001423856699191898</v>
       </c>
       <c r="H9" t="n">
-        <v>1.179047416318921</v>
+        <v>0.2029289863012877</v>
       </c>
       <c r="I9" t="n">
-        <v>1.170097272503994</v>
+        <v>0.0005440978180777927</v>
       </c>
       <c r="J9" t="n">
-        <v>1.281767599119579</v>
+        <v>0.0001853520704576996</v>
       </c>
       <c r="K9" t="n">
-        <v>1.225932435811786</v>
+        <v>0.0003647247430825981</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5006921664575085</v>
+        <v>0.003309274406698447</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6463436726376447</v>
+        <v>0.0119325466652844</v>
       </c>
       <c r="N9" t="n">
-        <v>1.021419463205538</v>
+        <v>1.000169306297265</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6738598608976812</v>
+        <v>0.01244053988060239</v>
       </c>
       <c r="P9" t="n">
-        <v>189.7456956626993</v>
+        <v>133.7139423932803</v>
       </c>
       <c r="Q9" t="n">
-        <v>304.3200232003101</v>
+        <v>204.4087402356359</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_8</t>
+          <t>model_25_6_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9335194213597257</v>
+        <v>0.9997571228194747</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8191621276080322</v>
+        <v>0.6581571720486163</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5885131264432075</v>
+        <v>0.9995514815774841</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8683181157203527</v>
+        <v>0.9991991342319948</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8220449667929155</v>
+        <v>0.9994945666021865</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4445559354824319</v>
+        <v>0.0001441823861077259</v>
       </c>
       <c r="H10" t="n">
-        <v>1.209263685366926</v>
+        <v>0.2029326695132116</v>
       </c>
       <c r="I10" t="n">
-        <v>1.267036893170529</v>
+        <v>0.0005227090269153109</v>
       </c>
       <c r="J10" t="n">
-        <v>1.38245652571797</v>
+        <v>0.0001803162368609233</v>
       </c>
       <c r="K10" t="n">
-        <v>1.324746636434174</v>
+        <v>0.0003515126318881171</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5099327147199196</v>
+        <v>0.003434727017947255</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6667502797018026</v>
+        <v>0.01200759701637784</v>
       </c>
       <c r="N10" t="n">
-        <v>1.022793341248094</v>
+        <v>1.000171442715665</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6951352194720603</v>
+        <v>0.01251878528051752</v>
       </c>
       <c r="P10" t="n">
-        <v>189.6213587856793</v>
+        <v>133.6888629792383</v>
       </c>
       <c r="Q10" t="n">
-        <v>304.1956863232901</v>
+        <v>204.3836608215939</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_9</t>
+          <t>model_25_6_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9297335326369689</v>
+        <v>0.9997523778764168</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8148938496588274</v>
+        <v>0.6581493073155364</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5592736766482063</v>
+        <v>0.9995715699851829</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8594938219354815</v>
+        <v>0.9992234364644622</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8097755031947473</v>
+        <v>0.999515332033306</v>
       </c>
       <c r="G11" t="n">
-        <v>0.469872190803921</v>
+        <v>0.0001469991892777577</v>
       </c>
       <c r="H11" t="n">
-        <v>1.237805679666871</v>
+        <v>0.2029373383585066</v>
       </c>
       <c r="I11" t="n">
-        <v>1.357070048556617</v>
+        <v>0.0004992977432011563</v>
       </c>
       <c r="J11" t="n">
-        <v>1.475097989610153</v>
+        <v>0.0001748445494934421</v>
       </c>
       <c r="K11" t="n">
-        <v>1.416083927319395</v>
+        <v>0.0003370709440679153</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5180854366753693</v>
+        <v>0.003573689056800569</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6854722392656912</v>
+        <v>0.01212432221931427</v>
       </c>
       <c r="N11" t="n">
-        <v>1.024091360238754</v>
+        <v>1.000174792087235</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7146542116143828</v>
+        <v>0.01264047971699744</v>
       </c>
       <c r="P11" t="n">
-        <v>189.5105891114373</v>
+        <v>133.6501669726361</v>
       </c>
       <c r="Q11" t="n">
-        <v>304.0849166490481</v>
+        <v>204.3449648149917</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_10</t>
+          <t>model_25_6_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9261820739973721</v>
+        <v>0.9997453997664003</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8108907349469892</v>
+        <v>0.6581392110867005</v>
       </c>
       <c r="D12" t="n">
-        <v>0.532220700887721</v>
+        <v>0.9995934788449131</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8514023360324444</v>
+        <v>0.9992499446231392</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7984749418718349</v>
+        <v>0.9995379821304718</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4936208110798687</v>
+        <v>0.0001511416968221939</v>
       </c>
       <c r="H12" t="n">
-        <v>1.264574526177582</v>
+        <v>0.202943331916078</v>
       </c>
       <c r="I12" t="n">
-        <v>1.440370684764765</v>
+        <v>0.0004737648817276245</v>
       </c>
       <c r="J12" t="n">
-        <v>1.560046101877844</v>
+        <v>0.0001688761942337922</v>
       </c>
       <c r="K12" t="n">
-        <v>1.500208440869544</v>
+        <v>0.0003213185317783263</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5253078899448628</v>
+        <v>0.003727646625864616</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7025815334036817</v>
+        <v>0.01229396993742029</v>
       </c>
       <c r="N12" t="n">
-        <v>1.025309003200901</v>
+        <v>1.000179717811953</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7324918838249489</v>
+        <v>0.01281734968968242</v>
       </c>
       <c r="P12" t="n">
-        <v>189.4119752908971</v>
+        <v>133.5945855432213</v>
       </c>
       <c r="Q12" t="n">
-        <v>303.986302828508</v>
+        <v>204.2893833855769</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_11</t>
+          <t>model_25_6_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9228692487933766</v>
+        <v>0.999735522874123</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8071580194025223</v>
+        <v>0.6581268480346942</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5072701000767149</v>
+        <v>0.9996173253066528</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8440018143710308</v>
+        <v>0.9992785332188386</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7880964308003433</v>
+        <v>0.9995625869547524</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5157736884731436</v>
+        <v>0.000157005046737511</v>
       </c>
       <c r="H13" t="n">
-        <v>1.289535212211006</v>
+        <v>0.202950671157805</v>
       </c>
       <c r="I13" t="n">
-        <v>1.517197756940986</v>
+        <v>0.0004459739144327358</v>
       </c>
       <c r="J13" t="n">
-        <v>1.637740156154979</v>
+        <v>0.0001624394251775882</v>
       </c>
       <c r="K13" t="n">
-        <v>1.577468956547983</v>
+        <v>0.000304206669805162</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5317155823953515</v>
+        <v>0.003898175411989431</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7181738567179563</v>
+        <v>0.01253016547127415</v>
       </c>
       <c r="N13" t="n">
-        <v>1.026444828985128</v>
+        <v>1.000186689735913</v>
       </c>
       <c r="O13" t="n">
-        <v>0.7487480046232711</v>
+        <v>0.0130636005564046</v>
       </c>
       <c r="P13" t="n">
-        <v>189.3241743958777</v>
+        <v>133.5184652166154</v>
       </c>
       <c r="Q13" t="n">
-        <v>303.8985019334885</v>
+        <v>204.213263058971</v>
       </c>
     </row>
     <row r="14">
@@ -1177,217 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9197939255718675</v>
+        <v>0.9997219194250136</v>
       </c>
       <c r="C14" t="n">
-        <v>0.803693980858561</v>
+        <v>0.6581113847084847</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4843233197249097</v>
+        <v>0.9996431589190311</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8372489986102936</v>
+        <v>0.9993092149156555</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7785890597656264</v>
+        <v>0.9995891981431838</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5363383890159369</v>
+        <v>0.0001650806417672414</v>
       </c>
       <c r="H14" t="n">
-        <v>1.312699253904906</v>
+        <v>0.2029598508562239</v>
       </c>
       <c r="I14" t="n">
-        <v>1.587854730841285</v>
+        <v>0.0004158670967189241</v>
       </c>
       <c r="J14" t="n">
-        <v>1.708634298249551</v>
+        <v>0.0001555313909831708</v>
       </c>
       <c r="K14" t="n">
-        <v>1.648244464116327</v>
+        <v>0.0002856994462547763</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5374124283092987</v>
+        <v>0.004086739654518472</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7323512743321587</v>
+        <v>0.0128483711717572</v>
       </c>
       <c r="N14" t="n">
-        <v>1.027499225518217</v>
+        <v>1.000196292170579</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7635289842566105</v>
+        <v>0.01339535293233382</v>
       </c>
       <c r="P14" t="n">
-        <v>189.2459799886416</v>
+        <v>133.4181529309478</v>
       </c>
       <c r="Q14" t="n">
-        <v>303.8203075262525</v>
+        <v>204.1129507733035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_13</t>
+          <t>model_25_6_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9169500546975714</v>
+        <v>0.9997035433873603</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8004920780680514</v>
+        <v>0.6580927686815802</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4632703608661792</v>
+        <v>0.999671000310814</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8310972481748502</v>
+        <v>0.999342139242236</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7698971350192592</v>
+        <v>0.999617857740751</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5553553666471757</v>
+        <v>0.0001759894515217645</v>
       </c>
       <c r="H15" t="n">
-        <v>1.33411039260845</v>
+        <v>0.2029709021339649</v>
       </c>
       <c r="I15" t="n">
-        <v>1.652680311676566</v>
+        <v>0.0003834203875621067</v>
       </c>
       <c r="J15" t="n">
-        <v>1.773218182210434</v>
+        <v>0.0001481184250313697</v>
       </c>
       <c r="K15" t="n">
-        <v>1.712949563288709</v>
+        <v>0.0002657676201956267</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5424843461160475</v>
+        <v>0.004295570358380748</v>
       </c>
       <c r="M15" t="n">
-        <v>0.745221689597918</v>
+        <v>0.01326610159473251</v>
       </c>
       <c r="N15" t="n">
-        <v>1.028474266960833</v>
+        <v>1.000209263491275</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7769473197456657</v>
+        <v>0.01383086700423638</v>
       </c>
       <c r="P15" t="n">
-        <v>189.1762941397506</v>
+        <v>133.2901729985154</v>
       </c>
       <c r="Q15" t="n">
-        <v>303.7506216773614</v>
+        <v>203.984970840871</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_14</t>
+          <t>model_25_6_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9143289181924008</v>
+        <v>0.9996790847530428</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7975421708355905</v>
+        <v>0.6580709189061382</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4439921483368698</v>
+        <v>0.9997008126902501</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8255021961289694</v>
+        <v>0.9993770754860306</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7619648799817533</v>
+        <v>0.99964848871005</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5728829185264751</v>
+        <v>0.0001905091534106485</v>
       </c>
       <c r="H16" t="n">
-        <v>1.353836435854991</v>
+        <v>0.2029838731045284</v>
       </c>
       <c r="I16" t="n">
-        <v>1.712041151787657</v>
+        <v>0.0003486766645336036</v>
       </c>
       <c r="J16" t="n">
-        <v>1.831957592379666</v>
+        <v>0.0001402524726298902</v>
       </c>
       <c r="K16" t="n">
-        <v>1.771999470396678</v>
+        <v>0.0002444647686584483</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5470190199722924</v>
+        <v>0.00452693157755499</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7568902949083672</v>
+        <v>0.01380250533094077</v>
       </c>
       <c r="N16" t="n">
-        <v>1.029372942334034</v>
+        <v>1.000226528409617</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7891126817415235</v>
+        <v>0.01439010655800383</v>
       </c>
       <c r="P16" t="n">
-        <v>189.1141478276301</v>
+        <v>133.1316206303042</v>
       </c>
       <c r="Q16" t="n">
-        <v>303.688475365241</v>
+        <v>203.8264184726599</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_6_15</t>
+          <t>model_25_6_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9119202324761529</v>
+        <v>0.9996468826193364</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7948323567058664</v>
+        <v>0.6580456847144487</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4263740756444405</v>
+        <v>0.9997324425227615</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8204205165951021</v>
+        <v>0.9994137998617741</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7547379426413293</v>
+        <v>0.9996809350446553</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5889898110020022</v>
+        <v>0.0002096257310384708</v>
       </c>
       <c r="H17" t="n">
-        <v>1.371956975418003</v>
+        <v>0.2029988532107756</v>
       </c>
       <c r="I17" t="n">
-        <v>1.766290143729771</v>
+        <v>0.0003118148587671205</v>
       </c>
       <c r="J17" t="n">
-        <v>1.885307383595314</v>
+        <v>0.000131983919397022</v>
       </c>
       <c r="K17" t="n">
-        <v>1.825798796894548</v>
+        <v>0.0002218993890820712</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5510748578087097</v>
+        <v>0.004783319857785202</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7674567160446263</v>
+        <v>0.01447845748132275</v>
       </c>
       <c r="N17" t="n">
-        <v>1.030198777436748</v>
+        <v>1.000249259327527</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8001289373010604</v>
+        <v>0.01509483539084142</v>
       </c>
       <c r="P17" t="n">
-        <v>189.0586927885766</v>
+        <v>132.9403737009279</v>
       </c>
       <c r="Q17" t="n">
-        <v>303.6330203261875</v>
+        <v>203.6351715432836</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_8</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9996048305360333</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6580178173288282</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9997656385338318</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9994516395569445</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9997148741497975</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0002345896642425887</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2030153964946882</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0002731278087532016</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.0001234642501719552</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0001982958357274709</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.005067494766338137</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.01531632019261117</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.000278943151035</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.01596836765236431</v>
+      </c>
+      <c r="P18" t="n">
+        <v>132.7153453593048</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>203.4101432016604</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_7</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.9995503316993731</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6579881495183826</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9997999606695847</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.9994899480775603</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9997498321244477</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.000266942527911302</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2030330085885516</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0002331283588300774</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0001148390241314454</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0001739836914807614</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.005382583000800294</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.01633837592636741</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.00031741291809</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.01703393441465358</v>
+      </c>
+      <c r="P19" t="n">
+        <v>132.4569543480049</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>203.1517521903605</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.9994801179637141</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6579586171992251</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.9998347572485567</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9995273189373051</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9997850355979486</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0003086244344739352</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2030505402489332</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0001925759867949217</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.0001064249139688832</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0001495008106987268</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.00573708931806663</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.01756770999515689</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.000366975555025</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.01831560377982377</v>
+      </c>
+      <c r="P20" t="n">
+        <v>132.1667708854117</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>202.8615687277673</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_5</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.9993902409765277</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6579299214955656</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9998693712063915</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9995627275175639</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9998197697041572</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0003619792965514482</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2030675752582153</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0001522364437366595</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.845261424032959e-05</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.000125344359735137</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.006140118354036357</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.01902575350811232</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.000430418134216</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.01983571922369188</v>
+      </c>
+      <c r="P21" t="n">
+        <v>131.8478470792417</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>202.5426449215973</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_4</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.9992755756681466</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.6579050817379648</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9999026651521838</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.9995930175077261</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.9998525682675394</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0004300495768898463</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.2030823212113487</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.0001134352593624802</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9.163277343954671e-05</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0001025340164010134</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.006581302824698765</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.02073763672383732</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.000511358351897</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.02162048085199707</v>
+      </c>
+      <c r="P22" t="n">
+        <v>131.50322012166</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>202.1980179640156</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_3</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.9991300016378666</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.6578853432861095</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.9999333564647821</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.9996152844936075</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9998818877368009</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0005164686097347984</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2030940388090268</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7.766721654050756e-05</v>
+      </c>
+      <c r="J23" t="n">
+        <v>8.661932516796988e-05</v>
+      </c>
+      <c r="K23" t="n">
+        <v>8.214327085423871e-05</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.007063697627984863</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.02272594573906218</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.000614116490918</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.02369343629836712</v>
+      </c>
+      <c r="P23" t="n">
+        <v>131.1369920924166</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>201.8317899347722</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.9989459270016329</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6578706810841233</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.9999599934524149</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.9996252935322215</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.999905825199947</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0006257432654133684</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2031027429255</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.662413517177607e-05</v>
+      </c>
+      <c r="J24" t="n">
+        <v>8.436577376199711e-05</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.549553703294865e-05</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.007591223203963922</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.02501486089134554</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.000744051528259</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.02607979530739075</v>
+      </c>
+      <c r="P24" t="n">
+        <v>130.753140780268</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>201.4479386226236</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.9987141155341647</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6578598020776852</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.9999810273786255</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9996188642031094</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.999922408854493</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0007633565662364702</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2031092011736702</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.211093225792988e-05</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8.581334772177157e-05</v>
+      </c>
+      <c r="K25" t="n">
+        <v>5.396213998985072e-05</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.008169034964608985</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.02762890816222151</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.000907683152354</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.02880512798241174</v>
+      </c>
+      <c r="P25" t="n">
+        <v>130.3555706288593</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>201.0503684712149</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>model_25_6_0</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.9984232774783143</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6578439994675391</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9999949181712228</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.9995911311142733</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.999929557897598</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0009360105997390893</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2031185822856901</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.922427355869157e-06</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9.205749800917691e-05</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.899021101136009e-05</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.008803158002225798</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.03059429031272158</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1.001112980603543</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.03189675259024589</v>
+      </c>
+      <c r="P26" t="n">
+        <v>129.9477675140865</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>200.6425653564421</v>
       </c>
     </row>
   </sheetData>
